--- a/Part1_CoreBenchmarks_Results.xlsx
+++ b/Part1_CoreBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="490">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -1313,6 +1313,9 @@
   </si>
   <si>
     <t xml:space="preserve">64-bit Multiply (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
   </si>
   <si>
     <t xml:space="preserve">64-bit Divide (ops/ms)</t>
@@ -1608,23 +1611,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3601,7 +3604,9 @@
       <c r="B4" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="5" t="n">
+        <v>399.74</v>
+      </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -4032,7 +4037,9 @@
       <c r="B5" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="5" t="n">
+        <v>137.9</v>
+      </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -4463,7 +4470,9 @@
       <c r="B6" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="5" t="n">
+        <v>25.24</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4894,7 +4903,9 @@
       <c r="B7" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="C7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -5323,9 +5334,11 @@
         <v>426</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -5754,9 +5767,11 @@
         <v>426</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="C9" s="5"/>
+        <v>433</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -6185,9 +6200,11 @@
         <v>426</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="C10" s="5"/>
+        <v>434</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -6613,12 +6630,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C11" s="5"/>
+        <v>436</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>101.17</v>
+      </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -7044,12 +7063,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C12" s="5"/>
+        <v>437</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>90.65</v>
+      </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -7475,12 +7496,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C13" s="5"/>
+        <v>438</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>30.91</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -7906,12 +7929,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="C14" s="5"/>
+        <v>439</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>22.81</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -8337,12 +8362,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="C15" s="5"/>
+        <v>440</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.7</v>
+      </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -8768,12 +8795,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="C16" s="5"/>
+        <v>441</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -9199,12 +9228,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C17" s="5"/>
+        <v>442</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -9630,12 +9661,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="C18" s="5"/>
+        <v>443</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -10061,12 +10094,14 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C19" s="5"/>
+        <v>444</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -10492,12 +10527,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="C20" s="5"/>
+        <v>446</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>126.95</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -10923,12 +10960,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C21" s="5"/>
+        <v>447</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>97.5</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -11354,12 +11393,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C22" s="5"/>
+        <v>448</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>14.87</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -11785,12 +11826,14 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C23" s="5"/>
+        <v>449</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>29.95</v>
+      </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -12216,12 +12259,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C24" s="5"/>
+        <v>451</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1536.79</v>
+      </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -12647,12 +12692,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C25" s="5"/>
+        <v>452</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>489.67</v>
+      </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -13078,12 +13125,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C26" s="5"/>
+        <v>453</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>376.19</v>
+      </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -13509,12 +13558,14 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="C27" s="5"/>
+        <v>454</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1.96</v>
+      </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -13940,12 +13991,14 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C28" s="5"/>
+        <v>455</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -14371,12 +14424,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C29" s="5"/>
+        <v>456</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3.93</v>
+      </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -14802,12 +14857,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C30" s="5"/>
+        <v>457</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.51</v>
+      </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -15233,12 +15290,14 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C31" s="5"/>
+        <v>459</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.3</v>
+      </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -15664,12 +15723,14 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C32" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>285.71</v>
+      </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -16095,12 +16156,14 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="C33" s="5"/>
+        <v>461</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -16526,12 +16589,14 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="C34" s="5"/>
+        <v>462</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -16957,12 +17022,14 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C35" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -17388,12 +17455,14 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C36" s="5"/>
+        <v>459</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -17819,12 +17888,14 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C37" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -18250,12 +18321,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C38" s="5"/>
+        <v>466</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>217.77</v>
+      </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -18681,12 +18754,14 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C39" s="5"/>
+        <v>467</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>881.83</v>
+      </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -19112,12 +19187,14 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="C40" s="5"/>
+        <v>468</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>4.05</v>
+      </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -19543,12 +19620,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="C41" s="5"/>
+        <v>470</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>8.32</v>
+      </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -19974,12 +20053,14 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C42" s="5"/>
+        <v>471</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>78.28</v>
+      </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -20405,12 +20486,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="C43" s="5"/>
+        <v>473</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -20836,12 +20919,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C44" s="5"/>
+        <v>474</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -21267,12 +21352,14 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C45" s="5"/>
+        <v>475</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -21698,12 +21785,14 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C46" s="5"/>
+        <v>476</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -22129,12 +22218,14 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="C47" s="5"/>
+        <v>478</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>118.62</v>
+      </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -22560,12 +22651,14 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="C48" s="5"/>
+        <v>479</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>122.81</v>
+      </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -22991,12 +23084,14 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="C49" s="5"/>
+        <v>480</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>8.143</v>
+      </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -23422,12 +23517,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="C50" s="5"/>
+        <v>482</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>11.04</v>
+      </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -23853,12 +23950,14 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="C51" s="5"/>
+        <v>483</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>7.24</v>
+      </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
@@ -24284,12 +24383,14 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C52" s="5"/>
+        <v>484</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>3.8</v>
+      </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
@@ -24715,12 +24816,14 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C53" s="5"/>
+        <v>486</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>86.39</v>
+      </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
@@ -25146,12 +25249,14 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C54" s="5"/>
+        <v>487</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>135.21</v>
+      </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
@@ -25577,12 +25682,14 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C55" s="5"/>
+        <v>488</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>185.19</v>
+      </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
@@ -26008,12 +26115,14 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C56" s="5"/>
+        <v>489</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>226.65</v>
+      </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>

--- a/Part1_CoreBenchmarks_Results.xlsx
+++ b/Part1_CoreBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="492">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -1483,10 +1483,16 @@
     <t xml:space="preserve">1 MHz (KB/s)</t>
   </si>
   <si>
+    <t xml:space="preserve">2 MHz (KB/s)</t>
+  </si>
+  <si>
     <t xml:space="preserve">4 MHz (KB/s)</t>
   </si>
   <si>
-    <t xml:space="preserve">10 MHz (KB/s)</t>
+    <t xml:space="preserve">8 MHz (KB/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 MHz (KB/s)</t>
   </si>
   <si>
     <t xml:space="preserve">Bulk throughput (KB/s)</t>
@@ -1883,7 +1889,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PI56"/>
+  <dimension ref="A1:PI58"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.26"/>
@@ -3607,7 +3613,9 @@
       <c r="C4" s="5" t="n">
         <v>399.74</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5" t="n">
+        <v>5959.48</v>
+      </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -4040,7 +4048,9 @@
       <c r="C5" s="5" t="n">
         <v>137.9</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="5" t="n">
+        <v>4775.22</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -4473,7 +4483,9 @@
       <c r="C6" s="5" t="n">
         <v>25.24</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="5" t="n">
+        <v>3223.88</v>
+      </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -4906,7 +4918,9 @@
       <c r="C7" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -5339,7 +5353,9 @@
       <c r="C8" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -5772,7 +5788,9 @@
       <c r="C9" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -6205,7 +6223,9 @@
       <c r="C10" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -6638,7 +6658,9 @@
       <c r="C11" s="5" t="n">
         <v>101.17</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="5" t="n">
+        <v>6493.51</v>
+      </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -7071,7 +7093,9 @@
       <c r="C12" s="5" t="n">
         <v>90.65</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="5" t="n">
+        <v>5813.95</v>
+      </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -7504,7 +7528,9 @@
       <c r="C13" s="5" t="n">
         <v>30.91</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="5" t="n">
+        <v>2257.34</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -7937,7 +7963,9 @@
       <c r="C14" s="5" t="n">
         <v>22.81</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="5" t="n">
+        <v>782.93</v>
+      </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -8370,7 +8398,9 @@
       <c r="C15" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="5" t="n">
+        <v>179.43</v>
+      </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -8803,7 +8833,9 @@
       <c r="C16" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16" s="5" t="n">
+        <v>542.3</v>
+      </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -9236,7 +9268,9 @@
       <c r="C17" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="D17" s="5" t="n">
+        <v>67.21</v>
+      </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -9669,7 +9703,9 @@
       <c r="C18" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="5" t="n">
+        <v>39.31</v>
+      </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -10102,7 +10138,9 @@
       <c r="C19" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="5" t="n">
+        <v>10.59</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -10535,7 +10573,9 @@
       <c r="C20" s="5" t="n">
         <v>126.95</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20" s="5" t="n">
+        <v>328.99</v>
+      </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -10968,7 +11008,9 @@
       <c r="C21" s="5" t="n">
         <v>97.5</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="5" t="n">
+        <v>295.29</v>
+      </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -11401,7 +11443,9 @@
       <c r="C22" s="5" t="n">
         <v>14.87</v>
       </c>
-      <c r="D22" s="5"/>
+      <c r="D22" s="5" t="n">
+        <v>76.38</v>
+      </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -11834,7 +11878,9 @@
       <c r="C23" s="5" t="n">
         <v>29.95</v>
       </c>
-      <c r="D23" s="5"/>
+      <c r="D23" s="5" t="n">
+        <v>342.75</v>
+      </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -12267,7 +12313,9 @@
       <c r="C24" s="5" t="n">
         <v>1536.79</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24" s="5" t="n">
+        <v>7467.73</v>
+      </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -12700,7 +12748,9 @@
       <c r="C25" s="5" t="n">
         <v>489.67</v>
       </c>
-      <c r="D25" s="5"/>
+      <c r="D25" s="5" t="n">
+        <v>5085.42</v>
+      </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -13133,7 +13183,9 @@
       <c r="C26" s="5" t="n">
         <v>376.19</v>
       </c>
-      <c r="D26" s="5"/>
+      <c r="D26" s="5" t="n">
+        <v>4590.56</v>
+      </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -13566,7 +13618,9 @@
       <c r="C27" s="5" t="n">
         <v>1.96</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="5" t="n">
+        <v>6.83</v>
+      </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -13999,7 +14053,9 @@
       <c r="C28" s="5" t="n">
         <v>2.62</v>
       </c>
-      <c r="D28" s="5"/>
+      <c r="D28" s="5" t="n">
+        <v>6.84</v>
+      </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -14432,7 +14488,9 @@
       <c r="C29" s="5" t="n">
         <v>3.93</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="5" t="n">
+        <v>27.35</v>
+      </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -14865,7 +14923,9 @@
       <c r="C30" s="5" t="n">
         <v>1.51</v>
       </c>
-      <c r="D30" s="5"/>
+      <c r="D30" s="5" t="n">
+        <v>21.27</v>
+      </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -15298,7 +15358,9 @@
       <c r="C31" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="D31" s="5"/>
+      <c r="D31" s="5" t="n">
+        <v>1.58</v>
+      </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -15731,7 +15793,9 @@
       <c r="C32" s="5" t="n">
         <v>285.71</v>
       </c>
-      <c r="D32" s="5"/>
+      <c r="D32" s="5" t="n">
+        <v>37.98</v>
+      </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -16164,7 +16228,9 @@
       <c r="C33" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -16597,7 +16663,9 @@
       <c r="C34" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D34" s="5"/>
+      <c r="D34" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -17030,7 +17098,9 @@
       <c r="C35" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D35" s="5"/>
+      <c r="D35" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -17463,7 +17533,9 @@
       <c r="C36" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D36" s="5"/>
+      <c r="D36" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -17896,7 +17968,9 @@
       <c r="C37" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D37" s="5"/>
+      <c r="D37" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -18329,7 +18403,9 @@
       <c r="C38" s="5" t="n">
         <v>217.77</v>
       </c>
-      <c r="D38" s="5"/>
+      <c r="D38" s="5" t="n">
+        <v>1194.03</v>
+      </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -18762,7 +18838,9 @@
       <c r="C39" s="5" t="n">
         <v>881.83</v>
       </c>
-      <c r="D39" s="5"/>
+      <c r="D39" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -19195,7 +19273,9 @@
       <c r="C40" s="5" t="n">
         <v>4.05</v>
       </c>
-      <c r="D40" s="5"/>
+      <c r="D40" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -19628,7 +19708,9 @@
       <c r="C41" s="5" t="n">
         <v>8.32</v>
       </c>
-      <c r="D41" s="5"/>
+      <c r="D41" s="5" t="n">
+        <v>42.08</v>
+      </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -20061,7 +20143,9 @@
       <c r="C42" s="5" t="n">
         <v>78.28</v>
       </c>
-      <c r="D42" s="5"/>
+      <c r="D42" s="5" t="n">
+        <v>36.14</v>
+      </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -20494,7 +20578,9 @@
       <c r="C43" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D43" s="5"/>
+      <c r="D43" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -20927,7 +21013,9 @@
       <c r="C44" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -21360,7 +21448,9 @@
       <c r="C45" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D45" s="5"/>
+      <c r="D45" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -21793,7 +21883,9 @@
       <c r="C46" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="D46" s="5"/>
+      <c r="D46" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -22226,7 +22318,9 @@
       <c r="C47" s="5" t="n">
         <v>118.62</v>
       </c>
-      <c r="D47" s="5"/>
+      <c r="D47" s="5" t="n">
+        <v>39.05</v>
+      </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -22659,7 +22753,9 @@
       <c r="C48" s="5" t="n">
         <v>122.81</v>
       </c>
-      <c r="D48" s="5"/>
+      <c r="D48" s="5" t="n">
+        <v>39.18</v>
+      </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -23092,7 +23188,9 @@
       <c r="C49" s="5" t="n">
         <v>8.143</v>
       </c>
-      <c r="D49" s="5"/>
+      <c r="D49" s="5" t="n">
+        <v>25.52</v>
+      </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -23525,7 +23623,9 @@
       <c r="C50" s="5" t="n">
         <v>11.04</v>
       </c>
-      <c r="D50" s="5"/>
+      <c r="D50" s="5" t="n">
+        <v>5.49</v>
+      </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -23958,7 +24058,9 @@
       <c r="C51" s="5" t="n">
         <v>7.24</v>
       </c>
-      <c r="D51" s="5"/>
+      <c r="D51" s="5" t="n">
+        <v>5.53</v>
+      </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -24391,7 +24493,9 @@
       <c r="C52" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="D52" s="5"/>
+      <c r="D52" s="5" t="n">
+        <v>-0.04</v>
+      </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -24824,7 +24928,9 @@
       <c r="C53" s="5" t="n">
         <v>86.39</v>
       </c>
-      <c r="D53" s="5"/>
+      <c r="D53" s="5" t="n">
+        <v>94.78</v>
+      </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -25257,7 +25363,9 @@
       <c r="C54" s="5" t="n">
         <v>135.21</v>
       </c>
-      <c r="D54" s="5"/>
+      <c r="D54" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -25690,7 +25798,9 @@
       <c r="C55" s="5" t="n">
         <v>185.19</v>
       </c>
-      <c r="D55" s="5"/>
+      <c r="D55" s="5" t="n">
+        <v>227.27</v>
+      </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -26123,7 +26233,9 @@
       <c r="C56" s="5" t="n">
         <v>226.65</v>
       </c>
-      <c r="D56" s="5"/>
+      <c r="D56" s="5" t="n">
+        <v>294.55</v>
+      </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -26546,6 +26658,876 @@
       <c r="PH56" s="5"/>
       <c r="PI56" s="5"/>
     </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>318.07</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5"/>
+      <c r="S57" s="5"/>
+      <c r="T57" s="5"/>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="5"/>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5"/>
+      <c r="Z57" s="5"/>
+      <c r="AA57" s="5"/>
+      <c r="AB57" s="5"/>
+      <c r="AC57" s="5"/>
+      <c r="AD57" s="5"/>
+      <c r="AE57" s="5"/>
+      <c r="AF57" s="5"/>
+      <c r="AG57" s="5"/>
+      <c r="AH57" s="5"/>
+      <c r="AI57" s="5"/>
+      <c r="AJ57" s="5"/>
+      <c r="AK57" s="5"/>
+      <c r="AL57" s="5"/>
+      <c r="AM57" s="5"/>
+      <c r="AN57" s="5"/>
+      <c r="AO57" s="5"/>
+      <c r="AP57" s="5"/>
+      <c r="AQ57" s="5"/>
+      <c r="AR57" s="5"/>
+      <c r="AS57" s="5"/>
+      <c r="AT57" s="5"/>
+      <c r="AU57" s="5"/>
+      <c r="AV57" s="5"/>
+      <c r="AW57" s="5"/>
+      <c r="AX57" s="5"/>
+      <c r="AY57" s="5"/>
+      <c r="AZ57" s="5"/>
+      <c r="BA57" s="5"/>
+      <c r="BB57" s="5"/>
+      <c r="BC57" s="5"/>
+      <c r="BD57" s="5"/>
+      <c r="BE57" s="5"/>
+      <c r="BF57" s="5"/>
+      <c r="BG57" s="5"/>
+      <c r="BH57" s="5"/>
+      <c r="BI57" s="5"/>
+      <c r="BJ57" s="5"/>
+      <c r="BK57" s="5"/>
+      <c r="BL57" s="5"/>
+      <c r="BM57" s="5"/>
+      <c r="BN57" s="5"/>
+      <c r="BO57" s="5"/>
+      <c r="BP57" s="5"/>
+      <c r="BQ57" s="5"/>
+      <c r="BR57" s="5"/>
+      <c r="BS57" s="5"/>
+      <c r="BT57" s="5"/>
+      <c r="BU57" s="5"/>
+      <c r="BV57" s="5"/>
+      <c r="BW57" s="5"/>
+      <c r="BX57" s="5"/>
+      <c r="BY57" s="5"/>
+      <c r="BZ57" s="5"/>
+      <c r="CA57" s="5"/>
+      <c r="CB57" s="5"/>
+      <c r="CC57" s="5"/>
+      <c r="CD57" s="5"/>
+      <c r="CE57" s="5"/>
+      <c r="CF57" s="5"/>
+      <c r="CG57" s="5"/>
+      <c r="CH57" s="5"/>
+      <c r="CI57" s="5"/>
+      <c r="CJ57" s="5"/>
+      <c r="CK57" s="5"/>
+      <c r="CL57" s="5"/>
+      <c r="CM57" s="5"/>
+      <c r="CN57" s="5"/>
+      <c r="CO57" s="5"/>
+      <c r="CP57" s="5"/>
+      <c r="CQ57" s="5"/>
+      <c r="CR57" s="5"/>
+      <c r="CS57" s="5"/>
+      <c r="CT57" s="5"/>
+      <c r="CU57" s="5"/>
+      <c r="CV57" s="5"/>
+      <c r="CW57" s="5"/>
+      <c r="CX57" s="5"/>
+      <c r="CY57" s="5"/>
+      <c r="CZ57" s="5"/>
+      <c r="DA57" s="5"/>
+      <c r="DB57" s="5"/>
+      <c r="DC57" s="5"/>
+      <c r="DD57" s="5"/>
+      <c r="DE57" s="5"/>
+      <c r="DF57" s="5"/>
+      <c r="DG57" s="5"/>
+      <c r="DH57" s="5"/>
+      <c r="DI57" s="5"/>
+      <c r="DJ57" s="5"/>
+      <c r="DK57" s="5"/>
+      <c r="DL57" s="5"/>
+      <c r="DM57" s="5"/>
+      <c r="DN57" s="5"/>
+      <c r="DO57" s="5"/>
+      <c r="DP57" s="5"/>
+      <c r="DQ57" s="5"/>
+      <c r="DR57" s="5"/>
+      <c r="DS57" s="5"/>
+      <c r="DT57" s="5"/>
+      <c r="DU57" s="5"/>
+      <c r="DV57" s="5"/>
+      <c r="DW57" s="5"/>
+      <c r="DX57" s="5"/>
+      <c r="DY57" s="5"/>
+      <c r="DZ57" s="5"/>
+      <c r="EA57" s="5"/>
+      <c r="EB57" s="5"/>
+      <c r="EC57" s="5"/>
+      <c r="ED57" s="5"/>
+      <c r="EE57" s="5"/>
+      <c r="EF57" s="5"/>
+      <c r="EG57" s="5"/>
+      <c r="EH57" s="5"/>
+      <c r="EI57" s="5"/>
+      <c r="EJ57" s="5"/>
+      <c r="EK57" s="5"/>
+      <c r="EL57" s="5"/>
+      <c r="EM57" s="5"/>
+      <c r="EN57" s="5"/>
+      <c r="EO57" s="5"/>
+      <c r="EP57" s="5"/>
+      <c r="EQ57" s="5"/>
+      <c r="ER57" s="5"/>
+      <c r="ES57" s="5"/>
+      <c r="ET57" s="5"/>
+      <c r="EU57" s="5"/>
+      <c r="EV57" s="5"/>
+      <c r="EW57" s="5"/>
+      <c r="EX57" s="5"/>
+      <c r="EY57" s="5"/>
+      <c r="EZ57" s="5"/>
+      <c r="FA57" s="5"/>
+      <c r="FB57" s="5"/>
+      <c r="FC57" s="5"/>
+      <c r="FD57" s="5"/>
+      <c r="FE57" s="5"/>
+      <c r="FF57" s="5"/>
+      <c r="FG57" s="5"/>
+      <c r="FH57" s="5"/>
+      <c r="FI57" s="5"/>
+      <c r="FJ57" s="5"/>
+      <c r="FK57" s="5"/>
+      <c r="FL57" s="5"/>
+      <c r="FM57" s="5"/>
+      <c r="FN57" s="5"/>
+      <c r="FO57" s="5"/>
+      <c r="FP57" s="5"/>
+      <c r="FQ57" s="5"/>
+      <c r="FR57" s="5"/>
+      <c r="FS57" s="5"/>
+      <c r="FT57" s="5"/>
+      <c r="FU57" s="5"/>
+      <c r="FV57" s="5"/>
+      <c r="FW57" s="5"/>
+      <c r="FX57" s="5"/>
+      <c r="FY57" s="5"/>
+      <c r="FZ57" s="5"/>
+      <c r="GA57" s="5"/>
+      <c r="GB57" s="5"/>
+      <c r="GC57" s="5"/>
+      <c r="GD57" s="5"/>
+      <c r="GE57" s="5"/>
+      <c r="GF57" s="5"/>
+      <c r="GG57" s="5"/>
+      <c r="GH57" s="5"/>
+      <c r="GI57" s="5"/>
+      <c r="GJ57" s="5"/>
+      <c r="GK57" s="5"/>
+      <c r="GL57" s="5"/>
+      <c r="GM57" s="5"/>
+      <c r="GN57" s="5"/>
+      <c r="GO57" s="5"/>
+      <c r="GP57" s="5"/>
+      <c r="GQ57" s="5"/>
+      <c r="GR57" s="5"/>
+      <c r="GS57" s="5"/>
+      <c r="GT57" s="5"/>
+      <c r="GU57" s="5"/>
+      <c r="GV57" s="5"/>
+      <c r="GW57" s="5"/>
+      <c r="GX57" s="5"/>
+      <c r="GY57" s="5"/>
+      <c r="GZ57" s="5"/>
+      <c r="HA57" s="5"/>
+      <c r="HB57" s="5"/>
+      <c r="HC57" s="5"/>
+      <c r="HD57" s="5"/>
+      <c r="HE57" s="5"/>
+      <c r="HF57" s="5"/>
+      <c r="HG57" s="5"/>
+      <c r="HH57" s="5"/>
+      <c r="HI57" s="5"/>
+      <c r="HJ57" s="5"/>
+      <c r="HK57" s="5"/>
+      <c r="HL57" s="5"/>
+      <c r="HM57" s="5"/>
+      <c r="HN57" s="5"/>
+      <c r="HO57" s="5"/>
+      <c r="HP57" s="5"/>
+      <c r="HQ57" s="5"/>
+      <c r="HR57" s="5"/>
+      <c r="HS57" s="5"/>
+      <c r="HT57" s="5"/>
+      <c r="HU57" s="5"/>
+      <c r="HV57" s="5"/>
+      <c r="HW57" s="5"/>
+      <c r="HX57" s="5"/>
+      <c r="HY57" s="5"/>
+      <c r="HZ57" s="5"/>
+      <c r="IA57" s="5"/>
+      <c r="IB57" s="5"/>
+      <c r="IC57" s="5"/>
+      <c r="ID57" s="5"/>
+      <c r="IE57" s="5"/>
+      <c r="IF57" s="5"/>
+      <c r="IG57" s="5"/>
+      <c r="IH57" s="5"/>
+      <c r="II57" s="5"/>
+      <c r="IJ57" s="5"/>
+      <c r="IK57" s="5"/>
+      <c r="IL57" s="5"/>
+      <c r="IM57" s="5"/>
+      <c r="IN57" s="5"/>
+      <c r="IO57" s="5"/>
+      <c r="IP57" s="5"/>
+      <c r="IQ57" s="5"/>
+      <c r="IR57" s="5"/>
+      <c r="IS57" s="5"/>
+      <c r="IT57" s="5"/>
+      <c r="IU57" s="5"/>
+      <c r="IV57" s="5"/>
+      <c r="IW57" s="5"/>
+      <c r="IX57" s="5"/>
+      <c r="IY57" s="5"/>
+      <c r="IZ57" s="5"/>
+      <c r="JA57" s="5"/>
+      <c r="JB57" s="5"/>
+      <c r="JC57" s="5"/>
+      <c r="JD57" s="5"/>
+      <c r="JE57" s="5"/>
+      <c r="JF57" s="5"/>
+      <c r="JG57" s="5"/>
+      <c r="JH57" s="5"/>
+      <c r="JI57" s="5"/>
+      <c r="JJ57" s="5"/>
+      <c r="JK57" s="5"/>
+      <c r="JL57" s="5"/>
+      <c r="JM57" s="5"/>
+      <c r="JN57" s="5"/>
+      <c r="JO57" s="5"/>
+      <c r="JP57" s="5"/>
+      <c r="JQ57" s="5"/>
+      <c r="JR57" s="5"/>
+      <c r="JS57" s="5"/>
+      <c r="JT57" s="5"/>
+      <c r="JU57" s="5"/>
+      <c r="JV57" s="5"/>
+      <c r="JW57" s="5"/>
+      <c r="JX57" s="5"/>
+      <c r="JY57" s="5"/>
+      <c r="JZ57" s="5"/>
+      <c r="KA57" s="5"/>
+      <c r="KB57" s="5"/>
+      <c r="KC57" s="5"/>
+      <c r="KD57" s="5"/>
+      <c r="KE57" s="5"/>
+      <c r="KF57" s="5"/>
+      <c r="KG57" s="5"/>
+      <c r="KH57" s="5"/>
+      <c r="KI57" s="5"/>
+      <c r="KJ57" s="5"/>
+      <c r="KK57" s="5"/>
+      <c r="KL57" s="5"/>
+      <c r="KM57" s="5"/>
+      <c r="KN57" s="5"/>
+      <c r="KO57" s="5"/>
+      <c r="KP57" s="5"/>
+      <c r="KQ57" s="5"/>
+      <c r="KR57" s="5"/>
+      <c r="KS57" s="5"/>
+      <c r="KT57" s="5"/>
+      <c r="KU57" s="5"/>
+      <c r="KV57" s="5"/>
+      <c r="KW57" s="5"/>
+      <c r="KX57" s="5"/>
+      <c r="KY57" s="5"/>
+      <c r="KZ57" s="5"/>
+      <c r="LA57" s="5"/>
+      <c r="LB57" s="5"/>
+      <c r="LC57" s="5"/>
+      <c r="LD57" s="5"/>
+      <c r="LE57" s="5"/>
+      <c r="LF57" s="5"/>
+      <c r="LG57" s="5"/>
+      <c r="LH57" s="5"/>
+      <c r="LI57" s="5"/>
+      <c r="LJ57" s="5"/>
+      <c r="LK57" s="5"/>
+      <c r="LL57" s="5"/>
+      <c r="LM57" s="5"/>
+      <c r="LN57" s="5"/>
+      <c r="LO57" s="5"/>
+      <c r="LP57" s="5"/>
+      <c r="LQ57" s="5"/>
+      <c r="LR57" s="5"/>
+      <c r="LS57" s="5"/>
+      <c r="LT57" s="5"/>
+      <c r="LU57" s="5"/>
+      <c r="LV57" s="5"/>
+      <c r="LW57" s="5"/>
+      <c r="LX57" s="5"/>
+      <c r="LY57" s="5"/>
+      <c r="LZ57" s="5"/>
+      <c r="MA57" s="5"/>
+      <c r="MB57" s="5"/>
+      <c r="MC57" s="5"/>
+      <c r="MD57" s="5"/>
+      <c r="ME57" s="5"/>
+      <c r="MF57" s="5"/>
+      <c r="MG57" s="5"/>
+      <c r="MH57" s="5"/>
+      <c r="MI57" s="5"/>
+      <c r="MJ57" s="5"/>
+      <c r="MK57" s="5"/>
+      <c r="ML57" s="5"/>
+      <c r="MM57" s="5"/>
+      <c r="MN57" s="5"/>
+      <c r="MO57" s="5"/>
+      <c r="MP57" s="5"/>
+      <c r="MQ57" s="5"/>
+      <c r="MR57" s="5"/>
+      <c r="MS57" s="5"/>
+      <c r="MT57" s="5"/>
+      <c r="MU57" s="5"/>
+      <c r="MV57" s="5"/>
+      <c r="MW57" s="5"/>
+      <c r="MX57" s="5"/>
+      <c r="MY57" s="5"/>
+      <c r="MZ57" s="5"/>
+      <c r="NA57" s="5"/>
+      <c r="NB57" s="5"/>
+      <c r="NC57" s="5"/>
+      <c r="ND57" s="5"/>
+      <c r="NE57" s="5"/>
+      <c r="NF57" s="5"/>
+      <c r="NG57" s="5"/>
+      <c r="NH57" s="5"/>
+      <c r="NI57" s="5"/>
+      <c r="NJ57" s="5"/>
+      <c r="NK57" s="5"/>
+      <c r="NL57" s="5"/>
+      <c r="NM57" s="5"/>
+      <c r="NN57" s="5"/>
+      <c r="NO57" s="5"/>
+      <c r="NP57" s="5"/>
+      <c r="NQ57" s="5"/>
+      <c r="NR57" s="5"/>
+      <c r="NS57" s="5"/>
+      <c r="NT57" s="5"/>
+      <c r="NU57" s="5"/>
+      <c r="NV57" s="5"/>
+      <c r="NW57" s="5"/>
+      <c r="NX57" s="5"/>
+      <c r="NY57" s="5"/>
+      <c r="NZ57" s="5"/>
+      <c r="OA57" s="5"/>
+      <c r="OB57" s="5"/>
+      <c r="OC57" s="5"/>
+      <c r="OD57" s="5"/>
+      <c r="OE57" s="5"/>
+      <c r="OF57" s="5"/>
+      <c r="OG57" s="5"/>
+      <c r="OH57" s="5"/>
+      <c r="OI57" s="5"/>
+      <c r="OJ57" s="5"/>
+      <c r="OK57" s="5"/>
+      <c r="OL57" s="5"/>
+      <c r="OM57" s="5"/>
+      <c r="ON57" s="5"/>
+      <c r="OO57" s="5"/>
+      <c r="OP57" s="5"/>
+      <c r="OQ57" s="5"/>
+      <c r="OR57" s="5"/>
+      <c r="OS57" s="5"/>
+      <c r="OT57" s="5"/>
+      <c r="OU57" s="5"/>
+      <c r="OV57" s="5"/>
+      <c r="OW57" s="5"/>
+      <c r="OX57" s="5"/>
+      <c r="OY57" s="5"/>
+      <c r="OZ57" s="5"/>
+      <c r="PA57" s="5"/>
+      <c r="PB57" s="5"/>
+      <c r="PC57" s="5"/>
+      <c r="PD57" s="5"/>
+      <c r="PE57" s="5"/>
+      <c r="PF57" s="5"/>
+      <c r="PG57" s="5"/>
+      <c r="PH57" s="5"/>
+      <c r="PI57" s="5"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>448</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="5"/>
+      <c r="T58" s="5"/>
+      <c r="U58" s="5"/>
+      <c r="V58" s="5"/>
+      <c r="W58" s="5"/>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5"/>
+      <c r="Z58" s="5"/>
+      <c r="AA58" s="5"/>
+      <c r="AB58" s="5"/>
+      <c r="AC58" s="5"/>
+      <c r="AD58" s="5"/>
+      <c r="AE58" s="5"/>
+      <c r="AF58" s="5"/>
+      <c r="AG58" s="5"/>
+      <c r="AH58" s="5"/>
+      <c r="AI58" s="5"/>
+      <c r="AJ58" s="5"/>
+      <c r="AK58" s="5"/>
+      <c r="AL58" s="5"/>
+      <c r="AM58" s="5"/>
+      <c r="AN58" s="5"/>
+      <c r="AO58" s="5"/>
+      <c r="AP58" s="5"/>
+      <c r="AQ58" s="5"/>
+      <c r="AR58" s="5"/>
+      <c r="AS58" s="5"/>
+      <c r="AT58" s="5"/>
+      <c r="AU58" s="5"/>
+      <c r="AV58" s="5"/>
+      <c r="AW58" s="5"/>
+      <c r="AX58" s="5"/>
+      <c r="AY58" s="5"/>
+      <c r="AZ58" s="5"/>
+      <c r="BA58" s="5"/>
+      <c r="BB58" s="5"/>
+      <c r="BC58" s="5"/>
+      <c r="BD58" s="5"/>
+      <c r="BE58" s="5"/>
+      <c r="BF58" s="5"/>
+      <c r="BG58" s="5"/>
+      <c r="BH58" s="5"/>
+      <c r="BI58" s="5"/>
+      <c r="BJ58" s="5"/>
+      <c r="BK58" s="5"/>
+      <c r="BL58" s="5"/>
+      <c r="BM58" s="5"/>
+      <c r="BN58" s="5"/>
+      <c r="BO58" s="5"/>
+      <c r="BP58" s="5"/>
+      <c r="BQ58" s="5"/>
+      <c r="BR58" s="5"/>
+      <c r="BS58" s="5"/>
+      <c r="BT58" s="5"/>
+      <c r="BU58" s="5"/>
+      <c r="BV58" s="5"/>
+      <c r="BW58" s="5"/>
+      <c r="BX58" s="5"/>
+      <c r="BY58" s="5"/>
+      <c r="BZ58" s="5"/>
+      <c r="CA58" s="5"/>
+      <c r="CB58" s="5"/>
+      <c r="CC58" s="5"/>
+      <c r="CD58" s="5"/>
+      <c r="CE58" s="5"/>
+      <c r="CF58" s="5"/>
+      <c r="CG58" s="5"/>
+      <c r="CH58" s="5"/>
+      <c r="CI58" s="5"/>
+      <c r="CJ58" s="5"/>
+      <c r="CK58" s="5"/>
+      <c r="CL58" s="5"/>
+      <c r="CM58" s="5"/>
+      <c r="CN58" s="5"/>
+      <c r="CO58" s="5"/>
+      <c r="CP58" s="5"/>
+      <c r="CQ58" s="5"/>
+      <c r="CR58" s="5"/>
+      <c r="CS58" s="5"/>
+      <c r="CT58" s="5"/>
+      <c r="CU58" s="5"/>
+      <c r="CV58" s="5"/>
+      <c r="CW58" s="5"/>
+      <c r="CX58" s="5"/>
+      <c r="CY58" s="5"/>
+      <c r="CZ58" s="5"/>
+      <c r="DA58" s="5"/>
+      <c r="DB58" s="5"/>
+      <c r="DC58" s="5"/>
+      <c r="DD58" s="5"/>
+      <c r="DE58" s="5"/>
+      <c r="DF58" s="5"/>
+      <c r="DG58" s="5"/>
+      <c r="DH58" s="5"/>
+      <c r="DI58" s="5"/>
+      <c r="DJ58" s="5"/>
+      <c r="DK58" s="5"/>
+      <c r="DL58" s="5"/>
+      <c r="DM58" s="5"/>
+      <c r="DN58" s="5"/>
+      <c r="DO58" s="5"/>
+      <c r="DP58" s="5"/>
+      <c r="DQ58" s="5"/>
+      <c r="DR58" s="5"/>
+      <c r="DS58" s="5"/>
+      <c r="DT58" s="5"/>
+      <c r="DU58" s="5"/>
+      <c r="DV58" s="5"/>
+      <c r="DW58" s="5"/>
+      <c r="DX58" s="5"/>
+      <c r="DY58" s="5"/>
+      <c r="DZ58" s="5"/>
+      <c r="EA58" s="5"/>
+      <c r="EB58" s="5"/>
+      <c r="EC58" s="5"/>
+      <c r="ED58" s="5"/>
+      <c r="EE58" s="5"/>
+      <c r="EF58" s="5"/>
+      <c r="EG58" s="5"/>
+      <c r="EH58" s="5"/>
+      <c r="EI58" s="5"/>
+      <c r="EJ58" s="5"/>
+      <c r="EK58" s="5"/>
+      <c r="EL58" s="5"/>
+      <c r="EM58" s="5"/>
+      <c r="EN58" s="5"/>
+      <c r="EO58" s="5"/>
+      <c r="EP58" s="5"/>
+      <c r="EQ58" s="5"/>
+      <c r="ER58" s="5"/>
+      <c r="ES58" s="5"/>
+      <c r="ET58" s="5"/>
+      <c r="EU58" s="5"/>
+      <c r="EV58" s="5"/>
+      <c r="EW58" s="5"/>
+      <c r="EX58" s="5"/>
+      <c r="EY58" s="5"/>
+      <c r="EZ58" s="5"/>
+      <c r="FA58" s="5"/>
+      <c r="FB58" s="5"/>
+      <c r="FC58" s="5"/>
+      <c r="FD58" s="5"/>
+      <c r="FE58" s="5"/>
+      <c r="FF58" s="5"/>
+      <c r="FG58" s="5"/>
+      <c r="FH58" s="5"/>
+      <c r="FI58" s="5"/>
+      <c r="FJ58" s="5"/>
+      <c r="FK58" s="5"/>
+      <c r="FL58" s="5"/>
+      <c r="FM58" s="5"/>
+      <c r="FN58" s="5"/>
+      <c r="FO58" s="5"/>
+      <c r="FP58" s="5"/>
+      <c r="FQ58" s="5"/>
+      <c r="FR58" s="5"/>
+      <c r="FS58" s="5"/>
+      <c r="FT58" s="5"/>
+      <c r="FU58" s="5"/>
+      <c r="FV58" s="5"/>
+      <c r="FW58" s="5"/>
+      <c r="FX58" s="5"/>
+      <c r="FY58" s="5"/>
+      <c r="FZ58" s="5"/>
+      <c r="GA58" s="5"/>
+      <c r="GB58" s="5"/>
+      <c r="GC58" s="5"/>
+      <c r="GD58" s="5"/>
+      <c r="GE58" s="5"/>
+      <c r="GF58" s="5"/>
+      <c r="GG58" s="5"/>
+      <c r="GH58" s="5"/>
+      <c r="GI58" s="5"/>
+      <c r="GJ58" s="5"/>
+      <c r="GK58" s="5"/>
+      <c r="GL58" s="5"/>
+      <c r="GM58" s="5"/>
+      <c r="GN58" s="5"/>
+      <c r="GO58" s="5"/>
+      <c r="GP58" s="5"/>
+      <c r="GQ58" s="5"/>
+      <c r="GR58" s="5"/>
+      <c r="GS58" s="5"/>
+      <c r="GT58" s="5"/>
+      <c r="GU58" s="5"/>
+      <c r="GV58" s="5"/>
+      <c r="GW58" s="5"/>
+      <c r="GX58" s="5"/>
+      <c r="GY58" s="5"/>
+      <c r="GZ58" s="5"/>
+      <c r="HA58" s="5"/>
+      <c r="HB58" s="5"/>
+      <c r="HC58" s="5"/>
+      <c r="HD58" s="5"/>
+      <c r="HE58" s="5"/>
+      <c r="HF58" s="5"/>
+      <c r="HG58" s="5"/>
+      <c r="HH58" s="5"/>
+      <c r="HI58" s="5"/>
+      <c r="HJ58" s="5"/>
+      <c r="HK58" s="5"/>
+      <c r="HL58" s="5"/>
+      <c r="HM58" s="5"/>
+      <c r="HN58" s="5"/>
+      <c r="HO58" s="5"/>
+      <c r="HP58" s="5"/>
+      <c r="HQ58" s="5"/>
+      <c r="HR58" s="5"/>
+      <c r="HS58" s="5"/>
+      <c r="HT58" s="5"/>
+      <c r="HU58" s="5"/>
+      <c r="HV58" s="5"/>
+      <c r="HW58" s="5"/>
+      <c r="HX58" s="5"/>
+      <c r="HY58" s="5"/>
+      <c r="HZ58" s="5"/>
+      <c r="IA58" s="5"/>
+      <c r="IB58" s="5"/>
+      <c r="IC58" s="5"/>
+      <c r="ID58" s="5"/>
+      <c r="IE58" s="5"/>
+      <c r="IF58" s="5"/>
+      <c r="IG58" s="5"/>
+      <c r="IH58" s="5"/>
+      <c r="II58" s="5"/>
+      <c r="IJ58" s="5"/>
+      <c r="IK58" s="5"/>
+      <c r="IL58" s="5"/>
+      <c r="IM58" s="5"/>
+      <c r="IN58" s="5"/>
+      <c r="IO58" s="5"/>
+      <c r="IP58" s="5"/>
+      <c r="IQ58" s="5"/>
+      <c r="IR58" s="5"/>
+      <c r="IS58" s="5"/>
+      <c r="IT58" s="5"/>
+      <c r="IU58" s="5"/>
+      <c r="IV58" s="5"/>
+      <c r="IW58" s="5"/>
+      <c r="IX58" s="5"/>
+      <c r="IY58" s="5"/>
+      <c r="IZ58" s="5"/>
+      <c r="JA58" s="5"/>
+      <c r="JB58" s="5"/>
+      <c r="JC58" s="5"/>
+      <c r="JD58" s="5"/>
+      <c r="JE58" s="5"/>
+      <c r="JF58" s="5"/>
+      <c r="JG58" s="5"/>
+      <c r="JH58" s="5"/>
+      <c r="JI58" s="5"/>
+      <c r="JJ58" s="5"/>
+      <c r="JK58" s="5"/>
+      <c r="JL58" s="5"/>
+      <c r="JM58" s="5"/>
+      <c r="JN58" s="5"/>
+      <c r="JO58" s="5"/>
+      <c r="JP58" s="5"/>
+      <c r="JQ58" s="5"/>
+      <c r="JR58" s="5"/>
+      <c r="JS58" s="5"/>
+      <c r="JT58" s="5"/>
+      <c r="JU58" s="5"/>
+      <c r="JV58" s="5"/>
+      <c r="JW58" s="5"/>
+      <c r="JX58" s="5"/>
+      <c r="JY58" s="5"/>
+      <c r="JZ58" s="5"/>
+      <c r="KA58" s="5"/>
+      <c r="KB58" s="5"/>
+      <c r="KC58" s="5"/>
+      <c r="KD58" s="5"/>
+      <c r="KE58" s="5"/>
+      <c r="KF58" s="5"/>
+      <c r="KG58" s="5"/>
+      <c r="KH58" s="5"/>
+      <c r="KI58" s="5"/>
+      <c r="KJ58" s="5"/>
+      <c r="KK58" s="5"/>
+      <c r="KL58" s="5"/>
+      <c r="KM58" s="5"/>
+      <c r="KN58" s="5"/>
+      <c r="KO58" s="5"/>
+      <c r="KP58" s="5"/>
+      <c r="KQ58" s="5"/>
+      <c r="KR58" s="5"/>
+      <c r="KS58" s="5"/>
+      <c r="KT58" s="5"/>
+      <c r="KU58" s="5"/>
+      <c r="KV58" s="5"/>
+      <c r="KW58" s="5"/>
+      <c r="KX58" s="5"/>
+      <c r="KY58" s="5"/>
+      <c r="KZ58" s="5"/>
+      <c r="LA58" s="5"/>
+      <c r="LB58" s="5"/>
+      <c r="LC58" s="5"/>
+      <c r="LD58" s="5"/>
+      <c r="LE58" s="5"/>
+      <c r="LF58" s="5"/>
+      <c r="LG58" s="5"/>
+      <c r="LH58" s="5"/>
+      <c r="LI58" s="5"/>
+      <c r="LJ58" s="5"/>
+      <c r="LK58" s="5"/>
+      <c r="LL58" s="5"/>
+      <c r="LM58" s="5"/>
+      <c r="LN58" s="5"/>
+      <c r="LO58" s="5"/>
+      <c r="LP58" s="5"/>
+      <c r="LQ58" s="5"/>
+      <c r="LR58" s="5"/>
+      <c r="LS58" s="5"/>
+      <c r="LT58" s="5"/>
+      <c r="LU58" s="5"/>
+      <c r="LV58" s="5"/>
+      <c r="LW58" s="5"/>
+      <c r="LX58" s="5"/>
+      <c r="LY58" s="5"/>
+      <c r="LZ58" s="5"/>
+      <c r="MA58" s="5"/>
+      <c r="MB58" s="5"/>
+      <c r="MC58" s="5"/>
+      <c r="MD58" s="5"/>
+      <c r="ME58" s="5"/>
+      <c r="MF58" s="5"/>
+      <c r="MG58" s="5"/>
+      <c r="MH58" s="5"/>
+      <c r="MI58" s="5"/>
+      <c r="MJ58" s="5"/>
+      <c r="MK58" s="5"/>
+      <c r="ML58" s="5"/>
+      <c r="MM58" s="5"/>
+      <c r="MN58" s="5"/>
+      <c r="MO58" s="5"/>
+      <c r="MP58" s="5"/>
+      <c r="MQ58" s="5"/>
+      <c r="MR58" s="5"/>
+      <c r="MS58" s="5"/>
+      <c r="MT58" s="5"/>
+      <c r="MU58" s="5"/>
+      <c r="MV58" s="5"/>
+      <c r="MW58" s="5"/>
+      <c r="MX58" s="5"/>
+      <c r="MY58" s="5"/>
+      <c r="MZ58" s="5"/>
+      <c r="NA58" s="5"/>
+      <c r="NB58" s="5"/>
+      <c r="NC58" s="5"/>
+      <c r="ND58" s="5"/>
+      <c r="NE58" s="5"/>
+      <c r="NF58" s="5"/>
+      <c r="NG58" s="5"/>
+      <c r="NH58" s="5"/>
+      <c r="NI58" s="5"/>
+      <c r="NJ58" s="5"/>
+      <c r="NK58" s="5"/>
+      <c r="NL58" s="5"/>
+      <c r="NM58" s="5"/>
+      <c r="NN58" s="5"/>
+      <c r="NO58" s="5"/>
+      <c r="NP58" s="5"/>
+      <c r="NQ58" s="5"/>
+      <c r="NR58" s="5"/>
+      <c r="NS58" s="5"/>
+      <c r="NT58" s="5"/>
+      <c r="NU58" s="5"/>
+      <c r="NV58" s="5"/>
+      <c r="NW58" s="5"/>
+      <c r="NX58" s="5"/>
+      <c r="NY58" s="5"/>
+      <c r="NZ58" s="5"/>
+      <c r="OA58" s="5"/>
+      <c r="OB58" s="5"/>
+      <c r="OC58" s="5"/>
+      <c r="OD58" s="5"/>
+      <c r="OE58" s="5"/>
+      <c r="OF58" s="5"/>
+      <c r="OG58" s="5"/>
+      <c r="OH58" s="5"/>
+      <c r="OI58" s="5"/>
+      <c r="OJ58" s="5"/>
+      <c r="OK58" s="5"/>
+      <c r="OL58" s="5"/>
+      <c r="OM58" s="5"/>
+      <c r="ON58" s="5"/>
+      <c r="OO58" s="5"/>
+      <c r="OP58" s="5"/>
+      <c r="OQ58" s="5"/>
+      <c r="OR58" s="5"/>
+      <c r="OS58" s="5"/>
+      <c r="OT58" s="5"/>
+      <c r="OU58" s="5"/>
+      <c r="OV58" s="5"/>
+      <c r="OW58" s="5"/>
+      <c r="OX58" s="5"/>
+      <c r="OY58" s="5"/>
+      <c r="OZ58" s="5"/>
+      <c r="PA58" s="5"/>
+      <c r="PB58" s="5"/>
+      <c r="PC58" s="5"/>
+      <c r="PD58" s="5"/>
+      <c r="PE58" s="5"/>
+      <c r="PF58" s="5"/>
+      <c r="PG58" s="5"/>
+      <c r="PH58" s="5"/>
+      <c r="PI58" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:PI1"/>

--- a/Part1_CoreBenchmarks_Results.xlsx
+++ b/Part1_CoreBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="492">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -3648,7 +3648,9 @@
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
+      <c r="AK4" s="5" t="n">
+        <v>405.58</v>
+      </c>
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
@@ -4083,7 +4085,9 @@
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="5"/>
-      <c r="AK5" s="5"/>
+      <c r="AK5" s="5" t="n">
+        <v>139.89</v>
+      </c>
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
@@ -4518,7 +4522,9 @@
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="5"/>
-      <c r="AK6" s="5"/>
+      <c r="AK6" s="5" t="n">
+        <v>25.47</v>
+      </c>
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
@@ -4953,7 +4959,9 @@
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
-      <c r="AK7" s="5"/>
+      <c r="AK7" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
@@ -5388,7 +5396,9 @@
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="5"/>
-      <c r="AK8" s="5"/>
+      <c r="AK8" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
@@ -5823,7 +5833,9 @@
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5"/>
-      <c r="AK9" s="5"/>
+      <c r="AK9" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
@@ -6258,7 +6270,9 @@
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="5"/>
-      <c r="AK10" s="5"/>
+      <c r="AK10" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
@@ -6693,7 +6707,9 @@
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="5"/>
-      <c r="AK11" s="5"/>
+      <c r="AK11" s="5" t="n">
+        <v>105.98</v>
+      </c>
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
@@ -7128,7 +7144,9 @@
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="5"/>
-      <c r="AK12" s="5"/>
+      <c r="AK12" s="5" t="n">
+        <v>90.84</v>
+      </c>
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
@@ -7563,7 +7581,9 @@
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
-      <c r="AK13" s="5"/>
+      <c r="AK13" s="5" t="n">
+        <v>30.81</v>
+      </c>
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
@@ -7998,7 +8018,9 @@
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
-      <c r="AK14" s="5"/>
+      <c r="AK14" s="5" t="n">
+        <v>22.89</v>
+      </c>
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
@@ -8433,7 +8455,9 @@
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
-      <c r="AK15" s="5"/>
+      <c r="AK15" s="5" t="n">
+        <v>3.68</v>
+      </c>
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
@@ -8868,7 +8892,9 @@
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
-      <c r="AK16" s="5"/>
+      <c r="AK16" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
@@ -9303,7 +9329,9 @@
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="5"/>
-      <c r="AK17" s="5"/>
+      <c r="AK17" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
@@ -9738,7 +9766,9 @@
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="5"/>
-      <c r="AK18" s="5"/>
+      <c r="AK18" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
@@ -10173,7 +10203,9 @@
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
-      <c r="AK19" s="5"/>
+      <c r="AK19" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
@@ -10608,7 +10640,9 @@
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
-      <c r="AK20" s="5"/>
+      <c r="AK20" s="5" t="n">
+        <v>129.17</v>
+      </c>
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
@@ -11043,7 +11077,9 @@
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="5"/>
-      <c r="AK21" s="5"/>
+      <c r="AK21" s="5" t="n">
+        <v>101.96</v>
+      </c>
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
@@ -11478,7 +11514,9 @@
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
-      <c r="AK22" s="5"/>
+      <c r="AK22" s="5" t="n">
+        <v>14.79</v>
+      </c>
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
@@ -11913,7 +11951,9 @@
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="5"/>
-      <c r="AK23" s="5"/>
+      <c r="AK23" s="5" t="n">
+        <v>29.79</v>
+      </c>
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
@@ -12348,7 +12388,9 @@
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="5"/>
-      <c r="AK24" s="5"/>
+      <c r="AK24" s="5" t="n">
+        <v>1680.19</v>
+      </c>
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
@@ -12783,7 +12825,9 @@
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="5"/>
-      <c r="AK25" s="5"/>
+      <c r="AK25" s="5" t="n">
+        <v>488.18</v>
+      </c>
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
@@ -13218,7 +13262,9 @@
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="5"/>
-      <c r="AK26" s="5"/>
+      <c r="AK26" s="5" t="n">
+        <v>374.27</v>
+      </c>
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
@@ -13653,7 +13699,9 @@
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="5"/>
-      <c r="AK27" s="5"/>
+      <c r="AK27" s="5" t="n">
+        <v>1.97</v>
+      </c>
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
@@ -14088,7 +14136,9 @@
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
-      <c r="AK28" s="5"/>
+      <c r="AK28" s="5" t="n">
+        <v>2.63</v>
+      </c>
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
@@ -14523,7 +14573,9 @@
       <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="5"/>
-      <c r="AK29" s="5"/>
+      <c r="AK29" s="5" t="n">
+        <v>3.95</v>
+      </c>
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
       <c r="AN29" s="5"/>
@@ -14958,7 +15010,9 @@
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="5"/>
-      <c r="AK30" s="5"/>
+      <c r="AK30" s="5" t="n">
+        <v>1.51</v>
+      </c>
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
       <c r="AN30" s="5"/>
@@ -15393,7 +15447,9 @@
       <c r="AH31" s="5"/>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="5"/>
-      <c r="AK31" s="5"/>
+      <c r="AK31" s="5" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
       <c r="AN31" s="5"/>
@@ -15828,7 +15884,9 @@
       <c r="AH32" s="5"/>
       <c r="AI32" s="5"/>
       <c r="AJ32" s="5"/>
-      <c r="AK32" s="5"/>
+      <c r="AK32" s="5" t="n">
+        <v>280.7</v>
+      </c>
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
@@ -16263,7 +16321,9 @@
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
-      <c r="AK33" s="5"/>
+      <c r="AK33" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
@@ -16698,7 +16758,9 @@
       <c r="AH34" s="5"/>
       <c r="AI34" s="5"/>
       <c r="AJ34" s="5"/>
-      <c r="AK34" s="5"/>
+      <c r="AK34" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
@@ -17133,7 +17195,9 @@
       <c r="AH35" s="5"/>
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
-      <c r="AK35" s="5"/>
+      <c r="AK35" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
@@ -17568,7 +17632,9 @@
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
       <c r="AJ36" s="5"/>
-      <c r="AK36" s="5"/>
+      <c r="AK36" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
@@ -18003,7 +18069,9 @@
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
-      <c r="AK37" s="5"/>
+      <c r="AK37" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
@@ -18438,7 +18506,9 @@
       <c r="AH38" s="5"/>
       <c r="AI38" s="5"/>
       <c r="AJ38" s="5"/>
-      <c r="AK38" s="5"/>
+      <c r="AK38" s="5" t="n">
+        <v>153.52</v>
+      </c>
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
@@ -18873,7 +18943,9 @@
       <c r="AH39" s="5"/>
       <c r="AI39" s="5"/>
       <c r="AJ39" s="5"/>
-      <c r="AK39" s="5"/>
+      <c r="AK39" s="5" t="n">
+        <v>1126.13</v>
+      </c>
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
@@ -19308,7 +19380,9 @@
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
       <c r="AJ40" s="5"/>
-      <c r="AK40" s="5"/>
+      <c r="AK40" s="5" t="n">
+        <v>7.34</v>
+      </c>
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
@@ -19743,7 +19817,9 @@
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
       <c r="AJ41" s="5"/>
-      <c r="AK41" s="5"/>
+      <c r="AK41" s="5" t="n">
+        <v>8.31</v>
+      </c>
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
@@ -20178,7 +20254,9 @@
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
       <c r="AJ42" s="5"/>
-      <c r="AK42" s="5"/>
+      <c r="AK42" s="5" t="n">
+        <v>72.8</v>
+      </c>
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
@@ -20613,7 +20691,9 @@
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
       <c r="AJ43" s="5"/>
-      <c r="AK43" s="5"/>
+      <c r="AK43" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
       <c r="AN43" s="5"/>
@@ -21048,7 +21128,9 @@
       <c r="AH44" s="5"/>
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
-      <c r="AK44" s="5"/>
+      <c r="AK44" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
       <c r="AN44" s="5"/>
@@ -21483,7 +21565,9 @@
       <c r="AH45" s="5"/>
       <c r="AI45" s="5"/>
       <c r="AJ45" s="5"/>
-      <c r="AK45" s="5"/>
+      <c r="AK45" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
       <c r="AN45" s="5"/>
@@ -21918,7 +22002,9 @@
       <c r="AH46" s="5"/>
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
-      <c r="AK46" s="5"/>
+      <c r="AK46" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
       <c r="AN46" s="5"/>
@@ -22353,7 +22439,9 @@
       <c r="AH47" s="5"/>
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
-      <c r="AK47" s="5"/>
+      <c r="AK47" s="5" t="n">
+        <v>104.53</v>
+      </c>
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
       <c r="AN47" s="5"/>
@@ -22788,7 +22876,9 @@
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
-      <c r="AK48" s="5"/>
+      <c r="AK48" s="5" t="n">
+        <v>107.38</v>
+      </c>
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
       <c r="AN48" s="5"/>
@@ -23223,7 +23313,9 @@
       <c r="AH49" s="5"/>
       <c r="AI49" s="5"/>
       <c r="AJ49" s="5"/>
-      <c r="AK49" s="5"/>
+      <c r="AK49" s="5" t="n">
+        <v>9.313</v>
+      </c>
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
       <c r="AN49" s="5"/>
@@ -23658,7 +23750,9 @@
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
-      <c r="AK50" s="5"/>
+      <c r="AK50" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
       <c r="AN50" s="5"/>
@@ -24093,7 +24187,9 @@
       <c r="AH51" s="5"/>
       <c r="AI51" s="5"/>
       <c r="AJ51" s="5"/>
-      <c r="AK51" s="5"/>
+      <c r="AK51" s="5" t="n">
+        <v>7.12</v>
+      </c>
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
       <c r="AN51" s="5"/>
@@ -24528,7 +24624,9 @@
       <c r="AH52" s="5"/>
       <c r="AI52" s="5"/>
       <c r="AJ52" s="5"/>
-      <c r="AK52" s="5"/>
+      <c r="AK52" s="5" t="n">
+        <v>4.88</v>
+      </c>
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
       <c r="AN52" s="5"/>
@@ -24963,7 +25061,9 @@
       <c r="AH53" s="5"/>
       <c r="AI53" s="5"/>
       <c r="AJ53" s="5"/>
-      <c r="AK53" s="5"/>
+      <c r="AK53" s="5" t="n">
+        <v>89.8</v>
+      </c>
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
       <c r="AN53" s="5"/>
@@ -25398,7 +25498,9 @@
       <c r="AH54" s="5"/>
       <c r="AI54" s="5"/>
       <c r="AJ54" s="5"/>
-      <c r="AK54" s="5"/>
+      <c r="AK54" s="5" t="n">
+        <v>140.13</v>
+      </c>
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
       <c r="AN54" s="5"/>
@@ -25833,7 +25935,9 @@
       <c r="AH55" s="5"/>
       <c r="AI55" s="5"/>
       <c r="AJ55" s="5"/>
-      <c r="AK55" s="5"/>
+      <c r="AK55" s="5" t="n">
+        <v>195.16</v>
+      </c>
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
       <c r="AN55" s="5"/>
@@ -26268,7 +26372,9 @@
       <c r="AH56" s="5"/>
       <c r="AI56" s="5"/>
       <c r="AJ56" s="5"/>
-      <c r="AK56" s="5"/>
+      <c r="AK56" s="5" t="n">
+        <v>243.19</v>
+      </c>
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
       <c r="AN56" s="5"/>
@@ -26703,7 +26809,9 @@
       <c r="AH57" s="5"/>
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
-      <c r="AK57" s="5"/>
+      <c r="AK57" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
       <c r="AN57" s="5"/>
@@ -27138,7 +27246,9 @@
       <c r="AH58" s="5"/>
       <c r="AI58" s="5"/>
       <c r="AJ58" s="5"/>
-      <c r="AK58" s="5"/>
+      <c r="AK58" s="5" t="n">
+        <v>405.5</v>
+      </c>
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
       <c r="AN58" s="5"/>

--- a/Part1_CoreBenchmarks_Results.xlsx
+++ b/Part1_CoreBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="492">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -3620,7 +3620,9 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5" t="n">
+        <v>19920.32</v>
+      </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -4057,7 +4059,9 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5" t="n">
+        <v>12987.01</v>
+      </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -4494,7 +4498,9 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5" t="n">
+        <v>9936.03</v>
+      </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -4931,7 +4937,9 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5" t="n">
+        <v>5783.06</v>
+      </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -5368,7 +5376,9 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5" t="n">
+        <v>1261.42</v>
+      </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -5805,7 +5815,9 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5" t="n">
+        <v>9259.26</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -6242,7 +6254,9 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5" t="n">
+        <v>10416.67</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -6679,7 +6693,9 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="I11" s="5" t="n">
+        <v>21739.13</v>
+      </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -7116,7 +7132,9 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="n">
+        <v>21739.13</v>
+      </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -7553,7 +7571,9 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="n">
+        <v>7874.02</v>
+      </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -7990,7 +8010,9 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -8427,7 +8449,9 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -8864,7 +8888,9 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -9301,7 +9327,9 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="I17" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
@@ -9738,7 +9766,9 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="I18" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -10175,7 +10205,9 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
@@ -10612,7 +10644,9 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5" t="n">
+        <v>1238.66</v>
+      </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
@@ -11049,7 +11083,9 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5" t="n">
+        <v>1028.52</v>
+      </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -11486,7 +11522,9 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5" t="n">
+        <v>117.23</v>
+      </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -11923,7 +11961,9 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="I23" s="5" t="n">
+        <v>1219.68</v>
+      </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -12360,7 +12400,9 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5" t="n">
+        <v>20207.83</v>
+      </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -12797,7 +12839,9 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5" t="n">
+        <v>13425.32</v>
+      </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
@@ -13234,7 +13278,9 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5" t="n">
+        <v>13417.3</v>
+      </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -13671,7 +13717,9 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="n">
+        <v>26.61</v>
+      </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
@@ -14108,7 +14156,9 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5" t="n">
+        <v>22.81</v>
+      </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -14545,7 +14595,9 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="I29" s="5" t="n">
+        <v>127.74</v>
+      </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
@@ -14982,7 +15034,9 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
+      <c r="I30" s="5" t="n">
+        <v>79.83</v>
+      </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
@@ -15419,7 +15473,9 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="I31" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
@@ -15856,7 +15912,9 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
+      <c r="I32" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
@@ -16293,7 +16351,9 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
+      <c r="I33" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
@@ -16730,7 +16790,9 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+      <c r="I34" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
@@ -17167,7 +17229,9 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+      <c r="I35" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
@@ -17604,7 +17668,9 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
+      <c r="I36" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
@@ -18041,7 +18107,9 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
@@ -18478,7 +18546,9 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+      <c r="I38" s="5" t="n">
+        <v>3546.1</v>
+      </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
@@ -18915,7 +18985,9 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
+      <c r="I39" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
@@ -19352,7 +19424,9 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
+      <c r="I40" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
@@ -19789,7 +19863,9 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="I41" s="5" t="n">
+        <v>29.09</v>
+      </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
@@ -20226,7 +20302,9 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
+      <c r="I42" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
@@ -20663,7 +20741,9 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
+      <c r="I43" s="5" t="n">
+        <v>2048</v>
+      </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
@@ -21100,7 +21180,9 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
+      <c r="I44" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
@@ -21537,7 +21619,9 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="I45" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
@@ -21974,7 +22058,9 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="I46" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
@@ -22411,7 +22497,9 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="I47" s="5" t="n">
+        <v>274.15</v>
+      </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
@@ -22848,7 +22936,9 @@
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="I48" s="5" t="n">
+        <v>274.8</v>
+      </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
@@ -23285,7 +23375,9 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="I49" s="5" t="n">
+        <v>3.639</v>
+      </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
@@ -23722,7 +23814,9 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
+      <c r="I50" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
@@ -24159,7 +24253,9 @@
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="I51" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
@@ -24596,7 +24692,9 @@
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
@@ -25033,7 +25131,9 @@
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
+      <c r="I53" s="5" t="n">
+        <v>35.72</v>
+      </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
@@ -25470,7 +25570,9 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
+      <c r="I54" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
@@ -25907,7 +26009,9 @@
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
+      <c r="I55" s="5" t="n">
+        <v>35.72</v>
+      </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
@@ -26344,7 +26448,9 @@
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
+      <c r="I56" s="5" t="n">
+        <v>35.72</v>
+      </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
@@ -26781,7 +26887,9 @@
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
+      <c r="I57" s="5" t="n">
+        <v>35.71</v>
+      </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
@@ -27218,7 +27326,9 @@
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
+      <c r="I58" s="5" t="n">
+        <v>51.4</v>
+      </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>

--- a/Part1_CoreBenchmarks_Results.xlsx
+++ b/Part1_CoreBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="492">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -3617,7 +3617,9 @@
         <v>5959.48</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5" t="n">
+        <v>399.68</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="n">
@@ -4056,7 +4058,9 @@
         <v>4775.22</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="n">
+        <v>137.9</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="n">
@@ -4495,7 +4499,9 @@
         <v>3223.88</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="n">
+        <v>25.25</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="n">
@@ -4934,7 +4940,9 @@
         <v>431</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="n">
@@ -5373,7 +5381,9 @@
         <v>431</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="n">
@@ -5812,7 +5822,9 @@
         <v>431</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="n">
@@ -6251,7 +6263,9 @@
         <v>431</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="n">
@@ -6690,7 +6704,9 @@
         <v>6493.51</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="n">
+        <v>101.21</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="n">
@@ -7129,7 +7145,9 @@
         <v>5813.95</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="n">
+        <v>90.65</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="n">
@@ -7568,7 +7586,9 @@
         <v>2257.34</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5" t="n">
+        <v>30.91</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5" t="n">
@@ -8007,7 +8027,9 @@
         <v>782.93</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="F14" s="5" t="n">
+        <v>22.8</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
@@ -8446,7 +8468,9 @@
         <v>179.43</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="n">
+        <v>3.7</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5" t="s">
@@ -8885,7 +8909,9 @@
         <v>542.3</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="F16" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
@@ -9324,7 +9350,9 @@
         <v>67.21</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
@@ -9763,7 +9791,9 @@
         <v>39.31</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
@@ -10202,7 +10232,9 @@
         <v>10.59</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
@@ -10641,7 +10673,9 @@
         <v>328.99</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="F20" s="5" t="n">
+        <v>126.95</v>
+      </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5" t="n">
@@ -11080,7 +11114,9 @@
         <v>295.29</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="F21" s="5" t="n">
+        <v>97.48</v>
+      </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5" t="n">
@@ -11519,7 +11555,9 @@
         <v>76.38</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="F22" s="5" t="n">
+        <v>14.87</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5" t="n">
@@ -11958,7 +11996,9 @@
         <v>342.75</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="F23" s="5" t="n">
+        <v>29.96</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5" t="n">
@@ -12397,7 +12437,9 @@
         <v>7467.73</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="F24" s="5" t="n">
+        <v>1536.79</v>
+      </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="n">
@@ -12836,7 +12878,9 @@
         <v>5085.42</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5" t="n">
+        <v>489.3</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5" t="n">
@@ -13275,7 +13319,9 @@
         <v>4590.56</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="F26" s="5" t="n">
+        <v>376.19</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5" t="n">
@@ -13714,7 +13760,9 @@
         <v>6.83</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5" t="n">
+        <v>1.96</v>
+      </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5" t="n">
@@ -14153,7 +14201,9 @@
         <v>6.84</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="n">
@@ -14592,7 +14642,9 @@
         <v>27.35</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="F29" s="5" t="n">
+        <v>3.93</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5" t="n">
@@ -15031,7 +15083,9 @@
         <v>21.27</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="F30" s="5" t="n">
+        <v>1.51</v>
+      </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5" t="n">
@@ -15470,7 +15524,9 @@
         <v>1.58</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="F31" s="5" t="n">
+        <v>0.3</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5" t="s">
@@ -15909,7 +15965,9 @@
         <v>37.98</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="F32" s="5" t="n">
+        <v>285.71</v>
+      </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
@@ -16348,7 +16406,9 @@
         <v>431</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5" t="s">
@@ -16787,7 +16847,9 @@
         <v>431</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5" t="s">
@@ -17226,7 +17288,9 @@
         <v>431</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
@@ -17665,7 +17729,9 @@
         <v>431</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
@@ -18104,7 +18170,9 @@
         <v>431</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="F37" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
@@ -18543,7 +18611,9 @@
         <v>1194.03</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="5" t="n">
+        <v>217.77</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="n">
@@ -18982,7 +19052,9 @@
         <v>431</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="F39" s="5" t="n">
+        <v>881.83</v>
+      </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
@@ -19421,7 +19493,9 @@
         <v>431</v>
       </c>
       <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="F40" s="5" t="n">
+        <v>4.05</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
@@ -19860,7 +19934,9 @@
         <v>42.08</v>
       </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="F41" s="5" t="n">
+        <v>8.32</v>
+      </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5" t="n">
@@ -20299,7 +20375,9 @@
         <v>36.14</v>
       </c>
       <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+      <c r="F42" s="5" t="n">
+        <v>78.22</v>
+      </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
@@ -20738,7 +20816,9 @@
         <v>431</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="F43" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="n">
@@ -21177,7 +21257,9 @@
         <v>431</v>
       </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
@@ -21616,7 +21698,9 @@
         <v>431</v>
       </c>
       <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
+      <c r="F45" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
@@ -22055,7 +22139,9 @@
         <v>431</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="F46" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
@@ -22494,7 +22580,9 @@
         <v>39.05</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="F47" s="5" t="n">
+        <v>118.61</v>
+      </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="n">
@@ -22933,7 +23021,9 @@
         <v>39.18</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="F48" s="5" t="n">
+        <v>122.81</v>
+      </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="n">
@@ -23372,7 +23462,9 @@
         <v>25.52</v>
       </c>
       <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="F49" s="5" t="n">
+        <v>8.143</v>
+      </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="n">
@@ -23811,7 +23903,9 @@
         <v>5.49</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="F50" s="5" t="n">
+        <v>11.32</v>
+      </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="n">
@@ -24250,7 +24344,9 @@
         <v>5.53</v>
       </c>
       <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="F51" s="5" t="n">
+        <v>7.4</v>
+      </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="n">
@@ -24689,7 +24785,9 @@
         <v>-0.04</v>
       </c>
       <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
+      <c r="F52" s="5" t="n">
+        <v>3.92</v>
+      </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="n">
@@ -25128,7 +25226,9 @@
         <v>94.78</v>
       </c>
       <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="F53" s="5" t="n">
+        <v>86.42</v>
+      </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="n">
@@ -25567,7 +25667,9 @@
         <v>431</v>
       </c>
       <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="F54" s="5" t="n">
+        <v>134.92</v>
+      </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
@@ -26006,7 +26108,9 @@
         <v>227.27</v>
       </c>
       <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="F55" s="5" t="n">
+        <v>185.05</v>
+      </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="n">
@@ -26445,7 +26549,9 @@
         <v>294.55</v>
       </c>
       <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="F56" s="5" t="n">
+        <v>226.86</v>
+      </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="n">
@@ -26884,7 +26990,9 @@
         <v>318.07</v>
       </c>
       <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="n">
@@ -27323,7 +27431,9 @@
         <v>448</v>
       </c>
       <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
+      <c r="F58" s="5" t="n">
+        <v>404.8</v>
+      </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="n">

--- a/Part1_CoreBenchmarks_Results.xlsx
+++ b/Part1_CoreBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="492">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 1: Core Benchmarks</t>
   </si>
@@ -4039,7 +4039,9 @@
       <c r="PC4" s="5"/>
       <c r="PD4" s="5"/>
       <c r="PE4" s="5"/>
-      <c r="PF4" s="5"/>
+      <c r="PF4" s="5" t="n">
+        <v>399.74</v>
+      </c>
       <c r="PG4" s="5"/>
       <c r="PH4" s="5"/>
       <c r="PI4" s="5"/>
@@ -4480,7 +4482,9 @@
       <c r="PC5" s="5"/>
       <c r="PD5" s="5"/>
       <c r="PE5" s="5"/>
-      <c r="PF5" s="5"/>
+      <c r="PF5" s="5" t="n">
+        <v>137.9</v>
+      </c>
       <c r="PG5" s="5"/>
       <c r="PH5" s="5"/>
       <c r="PI5" s="5"/>
@@ -4921,7 +4925,9 @@
       <c r="PC6" s="5"/>
       <c r="PD6" s="5"/>
       <c r="PE6" s="5"/>
-      <c r="PF6" s="5"/>
+      <c r="PF6" s="5" t="n">
+        <v>25.24</v>
+      </c>
       <c r="PG6" s="5"/>
       <c r="PH6" s="5"/>
       <c r="PI6" s="5"/>
@@ -5362,7 +5368,9 @@
       <c r="PC7" s="5"/>
       <c r="PD7" s="5"/>
       <c r="PE7" s="5"/>
-      <c r="PF7" s="5"/>
+      <c r="PF7" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG7" s="5"/>
       <c r="PH7" s="5"/>
       <c r="PI7" s="5"/>
@@ -5803,7 +5811,9 @@
       <c r="PC8" s="5"/>
       <c r="PD8" s="5"/>
       <c r="PE8" s="5"/>
-      <c r="PF8" s="5"/>
+      <c r="PF8" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG8" s="5"/>
       <c r="PH8" s="5"/>
       <c r="PI8" s="5"/>
@@ -6244,7 +6254,9 @@
       <c r="PC9" s="5"/>
       <c r="PD9" s="5"/>
       <c r="PE9" s="5"/>
-      <c r="PF9" s="5"/>
+      <c r="PF9" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG9" s="5"/>
       <c r="PH9" s="5"/>
       <c r="PI9" s="5"/>
@@ -6685,7 +6697,9 @@
       <c r="PC10" s="5"/>
       <c r="PD10" s="5"/>
       <c r="PE10" s="5"/>
-      <c r="PF10" s="5"/>
+      <c r="PF10" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG10" s="5"/>
       <c r="PH10" s="5"/>
       <c r="PI10" s="5"/>
@@ -7126,7 +7140,9 @@
       <c r="PC11" s="5"/>
       <c r="PD11" s="5"/>
       <c r="PE11" s="5"/>
-      <c r="PF11" s="5"/>
+      <c r="PF11" s="5" t="n">
+        <v>101.17</v>
+      </c>
       <c r="PG11" s="5"/>
       <c r="PH11" s="5"/>
       <c r="PI11" s="5"/>
@@ -7567,7 +7583,9 @@
       <c r="PC12" s="5"/>
       <c r="PD12" s="5"/>
       <c r="PE12" s="5"/>
-      <c r="PF12" s="5"/>
+      <c r="PF12" s="5" t="n">
+        <v>90.65</v>
+      </c>
       <c r="PG12" s="5"/>
       <c r="PH12" s="5"/>
       <c r="PI12" s="5"/>
@@ -8008,7 +8026,9 @@
       <c r="PC13" s="5"/>
       <c r="PD13" s="5"/>
       <c r="PE13" s="5"/>
-      <c r="PF13" s="5"/>
+      <c r="PF13" s="5" t="n">
+        <v>30.91</v>
+      </c>
       <c r="PG13" s="5"/>
       <c r="PH13" s="5"/>
       <c r="PI13" s="5"/>
@@ -8449,7 +8469,9 @@
       <c r="PC14" s="5"/>
       <c r="PD14" s="5"/>
       <c r="PE14" s="5"/>
-      <c r="PF14" s="5"/>
+      <c r="PF14" s="5" t="n">
+        <v>22.81</v>
+      </c>
       <c r="PG14" s="5"/>
       <c r="PH14" s="5"/>
       <c r="PI14" s="5"/>
@@ -8890,7 +8912,9 @@
       <c r="PC15" s="5"/>
       <c r="PD15" s="5"/>
       <c r="PE15" s="5"/>
-      <c r="PF15" s="5"/>
+      <c r="PF15" s="5" t="n">
+        <v>3.7</v>
+      </c>
       <c r="PG15" s="5"/>
       <c r="PH15" s="5"/>
       <c r="PI15" s="5"/>
@@ -9331,7 +9355,9 @@
       <c r="PC16" s="5"/>
       <c r="PD16" s="5"/>
       <c r="PE16" s="5"/>
-      <c r="PF16" s="5"/>
+      <c r="PF16" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG16" s="5"/>
       <c r="PH16" s="5"/>
       <c r="PI16" s="5"/>
@@ -9772,7 +9798,9 @@
       <c r="PC17" s="5"/>
       <c r="PD17" s="5"/>
       <c r="PE17" s="5"/>
-      <c r="PF17" s="5"/>
+      <c r="PF17" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG17" s="5"/>
       <c r="PH17" s="5"/>
       <c r="PI17" s="5"/>
@@ -10213,7 +10241,9 @@
       <c r="PC18" s="5"/>
       <c r="PD18" s="5"/>
       <c r="PE18" s="5"/>
-      <c r="PF18" s="5"/>
+      <c r="PF18" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG18" s="5"/>
       <c r="PH18" s="5"/>
       <c r="PI18" s="5"/>
@@ -10654,7 +10684,9 @@
       <c r="PC19" s="5"/>
       <c r="PD19" s="5"/>
       <c r="PE19" s="5"/>
-      <c r="PF19" s="5"/>
+      <c r="PF19" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG19" s="5"/>
       <c r="PH19" s="5"/>
       <c r="PI19" s="5"/>
@@ -11095,7 +11127,9 @@
       <c r="PC20" s="5"/>
       <c r="PD20" s="5"/>
       <c r="PE20" s="5"/>
-      <c r="PF20" s="5"/>
+      <c r="PF20" s="5" t="n">
+        <v>126.95</v>
+      </c>
       <c r="PG20" s="5"/>
       <c r="PH20" s="5"/>
       <c r="PI20" s="5"/>
@@ -11536,7 +11570,9 @@
       <c r="PC21" s="5"/>
       <c r="PD21" s="5"/>
       <c r="PE21" s="5"/>
-      <c r="PF21" s="5"/>
+      <c r="PF21" s="5" t="n">
+        <v>97.5</v>
+      </c>
       <c r="PG21" s="5"/>
       <c r="PH21" s="5"/>
       <c r="PI21" s="5"/>
@@ -11977,7 +12013,9 @@
       <c r="PC22" s="5"/>
       <c r="PD22" s="5"/>
       <c r="PE22" s="5"/>
-      <c r="PF22" s="5"/>
+      <c r="PF22" s="5" t="n">
+        <v>14.87</v>
+      </c>
       <c r="PG22" s="5"/>
       <c r="PH22" s="5"/>
       <c r="PI22" s="5"/>
@@ -12418,7 +12456,9 @@
       <c r="PC23" s="5"/>
       <c r="PD23" s="5"/>
       <c r="PE23" s="5"/>
-      <c r="PF23" s="5"/>
+      <c r="PF23" s="5" t="n">
+        <v>29.95</v>
+      </c>
       <c r="PG23" s="5"/>
       <c r="PH23" s="5"/>
       <c r="PI23" s="5"/>
@@ -12859,7 +12899,9 @@
       <c r="PC24" s="5"/>
       <c r="PD24" s="5"/>
       <c r="PE24" s="5"/>
-      <c r="PF24" s="5"/>
+      <c r="PF24" s="5" t="n">
+        <v>1536.79</v>
+      </c>
       <c r="PG24" s="5"/>
       <c r="PH24" s="5"/>
       <c r="PI24" s="5"/>
@@ -13300,7 +13342,9 @@
       <c r="PC25" s="5"/>
       <c r="PD25" s="5"/>
       <c r="PE25" s="5"/>
-      <c r="PF25" s="5"/>
+      <c r="PF25" s="5" t="n">
+        <v>489.67</v>
+      </c>
       <c r="PG25" s="5"/>
       <c r="PH25" s="5"/>
       <c r="PI25" s="5"/>
@@ -13741,7 +13785,9 @@
       <c r="PC26" s="5"/>
       <c r="PD26" s="5"/>
       <c r="PE26" s="5"/>
-      <c r="PF26" s="5"/>
+      <c r="PF26" s="5" t="n">
+        <v>376.19</v>
+      </c>
       <c r="PG26" s="5"/>
       <c r="PH26" s="5"/>
       <c r="PI26" s="5"/>
@@ -14182,7 +14228,9 @@
       <c r="PC27" s="5"/>
       <c r="PD27" s="5"/>
       <c r="PE27" s="5"/>
-      <c r="PF27" s="5"/>
+      <c r="PF27" s="5" t="n">
+        <v>1.96</v>
+      </c>
       <c r="PG27" s="5"/>
       <c r="PH27" s="5"/>
       <c r="PI27" s="5"/>
@@ -14623,7 +14671,9 @@
       <c r="PC28" s="5"/>
       <c r="PD28" s="5"/>
       <c r="PE28" s="5"/>
-      <c r="PF28" s="5"/>
+      <c r="PF28" s="5" t="n">
+        <v>2.62</v>
+      </c>
       <c r="PG28" s="5"/>
       <c r="PH28" s="5"/>
       <c r="PI28" s="5"/>
@@ -15064,7 +15114,9 @@
       <c r="PC29" s="5"/>
       <c r="PD29" s="5"/>
       <c r="PE29" s="5"/>
-      <c r="PF29" s="5"/>
+      <c r="PF29" s="5" t="n">
+        <v>3.93</v>
+      </c>
       <c r="PG29" s="5"/>
       <c r="PH29" s="5"/>
       <c r="PI29" s="5"/>
@@ -15505,7 +15557,9 @@
       <c r="PC30" s="5"/>
       <c r="PD30" s="5"/>
       <c r="PE30" s="5"/>
-      <c r="PF30" s="5"/>
+      <c r="PF30" s="5" t="n">
+        <v>1.51</v>
+      </c>
       <c r="PG30" s="5"/>
       <c r="PH30" s="5"/>
       <c r="PI30" s="5"/>
@@ -15946,7 +16000,9 @@
       <c r="PC31" s="5"/>
       <c r="PD31" s="5"/>
       <c r="PE31" s="5"/>
-      <c r="PF31" s="5"/>
+      <c r="PF31" s="5" t="n">
+        <v>0.3</v>
+      </c>
       <c r="PG31" s="5"/>
       <c r="PH31" s="5"/>
       <c r="PI31" s="5"/>
@@ -16387,7 +16443,9 @@
       <c r="PC32" s="5"/>
       <c r="PD32" s="5"/>
       <c r="PE32" s="5"/>
-      <c r="PF32" s="5"/>
+      <c r="PF32" s="5" t="n">
+        <v>285.71</v>
+      </c>
       <c r="PG32" s="5"/>
       <c r="PH32" s="5"/>
       <c r="PI32" s="5"/>
@@ -16828,7 +16886,9 @@
       <c r="PC33" s="5"/>
       <c r="PD33" s="5"/>
       <c r="PE33" s="5"/>
-      <c r="PF33" s="5"/>
+      <c r="PF33" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG33" s="5"/>
       <c r="PH33" s="5"/>
       <c r="PI33" s="5"/>
@@ -17269,7 +17329,9 @@
       <c r="PC34" s="5"/>
       <c r="PD34" s="5"/>
       <c r="PE34" s="5"/>
-      <c r="PF34" s="5"/>
+      <c r="PF34" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG34" s="5"/>
       <c r="PH34" s="5"/>
       <c r="PI34" s="5"/>
@@ -17710,7 +17772,9 @@
       <c r="PC35" s="5"/>
       <c r="PD35" s="5"/>
       <c r="PE35" s="5"/>
-      <c r="PF35" s="5"/>
+      <c r="PF35" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG35" s="5"/>
       <c r="PH35" s="5"/>
       <c r="PI35" s="5"/>
@@ -18151,7 +18215,9 @@
       <c r="PC36" s="5"/>
       <c r="PD36" s="5"/>
       <c r="PE36" s="5"/>
-      <c r="PF36" s="5"/>
+      <c r="PF36" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG36" s="5"/>
       <c r="PH36" s="5"/>
       <c r="PI36" s="5"/>
@@ -18592,7 +18658,9 @@
       <c r="PC37" s="5"/>
       <c r="PD37" s="5"/>
       <c r="PE37" s="5"/>
-      <c r="PF37" s="5"/>
+      <c r="PF37" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG37" s="5"/>
       <c r="PH37" s="5"/>
       <c r="PI37" s="5"/>
@@ -19033,7 +19101,9 @@
       <c r="PC38" s="5"/>
       <c r="PD38" s="5"/>
       <c r="PE38" s="5"/>
-      <c r="PF38" s="5"/>
+      <c r="PF38" s="5" t="n">
+        <v>217.77</v>
+      </c>
       <c r="PG38" s="5"/>
       <c r="PH38" s="5"/>
       <c r="PI38" s="5"/>
@@ -19474,7 +19544,9 @@
       <c r="PC39" s="5"/>
       <c r="PD39" s="5"/>
       <c r="PE39" s="5"/>
-      <c r="PF39" s="5"/>
+      <c r="PF39" s="5" t="n">
+        <v>881.32</v>
+      </c>
       <c r="PG39" s="5"/>
       <c r="PH39" s="5"/>
       <c r="PI39" s="5"/>
@@ -19915,7 +19987,9 @@
       <c r="PC40" s="5"/>
       <c r="PD40" s="5"/>
       <c r="PE40" s="5"/>
-      <c r="PF40" s="5"/>
+      <c r="PF40" s="5" t="n">
+        <v>4.05</v>
+      </c>
       <c r="PG40" s="5"/>
       <c r="PH40" s="5"/>
       <c r="PI40" s="5"/>
@@ -20356,7 +20430,9 @@
       <c r="PC41" s="5"/>
       <c r="PD41" s="5"/>
       <c r="PE41" s="5"/>
-      <c r="PF41" s="5"/>
+      <c r="PF41" s="5" t="n">
+        <v>8.32</v>
+      </c>
       <c r="PG41" s="5"/>
       <c r="PH41" s="5"/>
       <c r="PI41" s="5"/>
@@ -20797,7 +20873,9 @@
       <c r="PC42" s="5"/>
       <c r="PD42" s="5"/>
       <c r="PE42" s="5"/>
-      <c r="PF42" s="5"/>
+      <c r="PF42" s="5" t="n">
+        <v>78.22</v>
+      </c>
       <c r="PG42" s="5"/>
       <c r="PH42" s="5"/>
       <c r="PI42" s="5"/>
@@ -21238,7 +21316,9 @@
       <c r="PC43" s="5"/>
       <c r="PD43" s="5"/>
       <c r="PE43" s="5"/>
-      <c r="PF43" s="5"/>
+      <c r="PF43" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG43" s="5"/>
       <c r="PH43" s="5"/>
       <c r="PI43" s="5"/>
@@ -21679,7 +21759,9 @@
       <c r="PC44" s="5"/>
       <c r="PD44" s="5"/>
       <c r="PE44" s="5"/>
-      <c r="PF44" s="5"/>
+      <c r="PF44" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG44" s="5"/>
       <c r="PH44" s="5"/>
       <c r="PI44" s="5"/>
@@ -22120,7 +22202,9 @@
       <c r="PC45" s="5"/>
       <c r="PD45" s="5"/>
       <c r="PE45" s="5"/>
-      <c r="PF45" s="5"/>
+      <c r="PF45" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG45" s="5"/>
       <c r="PH45" s="5"/>
       <c r="PI45" s="5"/>
@@ -22561,7 +22645,9 @@
       <c r="PC46" s="5"/>
       <c r="PD46" s="5"/>
       <c r="PE46" s="5"/>
-      <c r="PF46" s="5"/>
+      <c r="PF46" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG46" s="5"/>
       <c r="PH46" s="5"/>
       <c r="PI46" s="5"/>
@@ -23002,7 +23088,9 @@
       <c r="PC47" s="5"/>
       <c r="PD47" s="5"/>
       <c r="PE47" s="5"/>
-      <c r="PF47" s="5"/>
+      <c r="PF47" s="5" t="n">
+        <v>118.6</v>
+      </c>
       <c r="PG47" s="5"/>
       <c r="PH47" s="5"/>
       <c r="PI47" s="5"/>
@@ -23443,7 +23531,9 @@
       <c r="PC48" s="5"/>
       <c r="PD48" s="5"/>
       <c r="PE48" s="5"/>
-      <c r="PF48" s="5"/>
+      <c r="PF48" s="5" t="n">
+        <v>122.81</v>
+      </c>
       <c r="PG48" s="5"/>
       <c r="PH48" s="5"/>
       <c r="PI48" s="5"/>
@@ -23884,7 +23974,9 @@
       <c r="PC49" s="5"/>
       <c r="PD49" s="5"/>
       <c r="PE49" s="5"/>
-      <c r="PF49" s="5"/>
+      <c r="PF49" s="5" t="n">
+        <v>8.143</v>
+      </c>
       <c r="PG49" s="5"/>
       <c r="PH49" s="5"/>
       <c r="PI49" s="5"/>
@@ -24325,7 +24417,9 @@
       <c r="PC50" s="5"/>
       <c r="PD50" s="5"/>
       <c r="PE50" s="5"/>
-      <c r="PF50" s="5"/>
+      <c r="PF50" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="PG50" s="5"/>
       <c r="PH50" s="5"/>
       <c r="PI50" s="5"/>
@@ -24766,7 +24860,9 @@
       <c r="PC51" s="5"/>
       <c r="PD51" s="5"/>
       <c r="PE51" s="5"/>
-      <c r="PF51" s="5"/>
+      <c r="PF51" s="5" t="n">
+        <v>7.4</v>
+      </c>
       <c r="PG51" s="5"/>
       <c r="PH51" s="5"/>
       <c r="PI51" s="5"/>
@@ -25207,7 +25303,9 @@
       <c r="PC52" s="5"/>
       <c r="PD52" s="5"/>
       <c r="PE52" s="5"/>
-      <c r="PF52" s="5"/>
+      <c r="PF52" s="5" t="n">
+        <v>3.8</v>
+      </c>
       <c r="PG52" s="5"/>
       <c r="PH52" s="5"/>
       <c r="PI52" s="5"/>
@@ -25648,7 +25746,9 @@
       <c r="PC53" s="5"/>
       <c r="PD53" s="5"/>
       <c r="PE53" s="5"/>
-      <c r="PF53" s="5"/>
+      <c r="PF53" s="5" t="n">
+        <v>86.36</v>
+      </c>
       <c r="PG53" s="5"/>
       <c r="PH53" s="5"/>
       <c r="PI53" s="5"/>
@@ -26089,7 +26189,9 @@
       <c r="PC54" s="5"/>
       <c r="PD54" s="5"/>
       <c r="PE54" s="5"/>
-      <c r="PF54" s="5"/>
+      <c r="PF54" s="5" t="n">
+        <v>134.99</v>
+      </c>
       <c r="PG54" s="5"/>
       <c r="PH54" s="5"/>
       <c r="PI54" s="5"/>
@@ -26530,7 +26632,9 @@
       <c r="PC55" s="5"/>
       <c r="PD55" s="5"/>
       <c r="PE55" s="5"/>
-      <c r="PF55" s="5"/>
+      <c r="PF55" s="5" t="n">
+        <v>184.91</v>
+      </c>
       <c r="PG55" s="5"/>
       <c r="PH55" s="5"/>
       <c r="PI55" s="5"/>
@@ -26971,7 +27075,9 @@
       <c r="PC56" s="5"/>
       <c r="PD56" s="5"/>
       <c r="PE56" s="5"/>
-      <c r="PF56" s="5"/>
+      <c r="PF56" s="5" t="n">
+        <v>226.86</v>
+      </c>
       <c r="PG56" s="5"/>
       <c r="PH56" s="5"/>
       <c r="PI56" s="5"/>
@@ -27412,7 +27518,9 @@
       <c r="PC57" s="5"/>
       <c r="PD57" s="5"/>
       <c r="PE57" s="5"/>
-      <c r="PF57" s="5"/>
+      <c r="PF57" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="PG57" s="5"/>
       <c r="PH57" s="5"/>
       <c r="PI57" s="5"/>
@@ -27853,7 +27961,9 @@
       <c r="PC58" s="5"/>
       <c r="PD58" s="5"/>
       <c r="PE58" s="5"/>
-      <c r="PF58" s="5"/>
+      <c r="PF58" s="5" t="n">
+        <v>404.7</v>
+      </c>
       <c r="PG58" s="5"/>
       <c r="PH58" s="5"/>
       <c r="PI58" s="5"/>
